--- a/registers/Разбор_архива_ВСН_Все.xlsx
+++ b/registers/Разбор_архива_ВСН_Все.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2039,6 +2039,56 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Дополнение к ВСН 009-88.pdf (вложение)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>взят</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Дополнение к ВСН 009-88</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>7 стр.; текстовый слой</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>РД 153-34.1-003-01.pdf (вложение)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>взят (не ВСН — в «Прочие НТД»)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>РД 153-34.1-003-01</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>139 стр.; текстовый слой</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
